--- a/領収書登録/領収書登録リスト.xlsx
+++ b/領収書登録/領収書登録リスト.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="31635" yWindow="3240" windowWidth="21600" windowHeight="12645"/>
+    <workbookView xWindow="2340" yWindow="3225" windowWidth="21600" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="領収書登録" state="visible" r:id="rId4"/>
@@ -35,16 +35,16 @@
     <t>スキャナ保存</t>
   </si>
   <si>
-    <t>D:\ClaudeDesktop\楽々申請\領収書登録\テスト領収書.pdf</t>
+    <t>D:\ClaudeDesktop\RegisterRakurakuSeisan\領収書登録\テスト領収書.pdf</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>D:\ClaudeDesktop\楽々申請\領収書登録\テスト領収書2.pdf</t>
-  </si>
-  <si>
-    <t>D:\ClaudeDesktop\楽々申請\領収書登録\テスト領収書3.pdf</t>
+    <t>D:\ClaudeDesktop\RegisterRakurakuSeisan\領収書登録\テスト領収書2.pdf</t>
+  </si>
+  <si>
+    <t>D:\ClaudeDesktop\RegisterRakurakuSeisan\領収書登録\テスト領収書3.pdf</t>
   </si>
   <si>
     <t>テスト領収書.pdf</t>
@@ -858,7 +858,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" ht="21.95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>4</v>
       </c>
@@ -872,7 +872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" ht="21.95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>4</v>
       </c>
@@ -886,7 +886,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" ht="21.95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>4</v>
       </c>
